--- a/data_raw/data_raw_2024_sheets/LTER2_BR_T04_2024.xlsx
+++ b/data_raw/data_raw_2024_sheets/LTER2_BR_T04_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/HLenihan 1/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryananderson/Reference/Bren/Coral Demography/data_raw/data_raw_2024_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{644D5042-4942-C640-95E2-F06B72A85D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557AD607-DED7-5841-9A51-45B51C8503AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="700" windowWidth="31420" windowHeight="23300" xr2:uid="{33000F0D-C049-684B-97A4-969A3BCCACE7}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="29920" windowHeight="18780" xr2:uid="{33000F0D-C049-684B-97A4-969A3BCCACE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="29">
   <si>
     <t>LTER2</t>
   </si>
@@ -198,6 +198,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -217,9 +224,14 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFA52A2A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -231,7 +243,19 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF159FEC"/>
+          <bgColor rgb="FFFB0006"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -243,7 +267,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF17A43F"/>
+          <bgColor rgb="FFB07EDD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -267,19 +291,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFB0006"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFA52A2A"/>
+          <bgColor rgb="FF17A43F"/>
         </patternFill>
       </fill>
     </dxf>
@@ -303,33 +315,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFB07EDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD4A6FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF49900"/>
+          <bgColor rgb="FF159FEC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -360,6 +346,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFD4A6FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFF49900"/>
         </patternFill>
       </fill>
@@ -368,6 +361,13 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF49900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1847,6 +1847,15 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
       <c r="D34" t="s">
         <v>3</v>
       </c>
@@ -1874,67 +1883,67 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:H2">
-    <cfRule type="beginsWith" dxfId="18" priority="8" operator="beginsWith" text="FI">
+    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="Missing data">
+      <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="17" priority="8" operator="beginsWith" text="FI">
       <formula>LEFT(A2,LEN("FI"))="FI"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="9" operator="containsText" text="Missing data">
-      <formula>NOT(ISERROR(SEARCH("Missing data",A2)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:M2">
+    <cfRule type="beginsWith" dxfId="16" priority="1" operator="beginsWith" text="UK">
+      <formula>LEFT(A2,LEN("UK"))="UK"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="15" priority="7" operator="beginsWith" text="FU">
+      <formula>LEFT(A2,LEN("FU"))="FU"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:K9 I11:K11 I20:K20 I27:K29 I32:K33 D34:G34 A3:H33">
-    <cfRule type="expression" dxfId="16" priority="10">
+  <conditionalFormatting sqref="I3:K9 A3:H33 I11:K11 I20:K20 I27:K29 I32:K33 A34:G34">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>A3="UK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>A3="Na"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:M2">
-    <cfRule type="beginsWith" dxfId="14" priority="1" operator="beginsWith" text="UK">
-      <formula>LEFT(A2,LEN("UK"))="UK"</formula>
+  <conditionalFormatting sqref="I3:K9 H3:H33 I11:K11 I20:K20 I27:K29 I32:K33">
+    <cfRule type="expression" dxfId="12" priority="19">
+      <formula>H3="Recruitment"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="13" priority="7" operator="beginsWith" text="FU">
-      <formula>LEFT(A2,LEN("FU"))="FU"</formula>
+    <cfRule type="beginsWith" dxfId="11" priority="14" operator="beginsWith" text="Fission">
+      <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H33 I3:K9 I11:K11 I20:K20 I27:K29 I32:K33">
-    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text=",">
+    <cfRule type="expression" dxfId="10" priority="18">
+      <formula>H3="Growth"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="17">
+      <formula>H3="Shrinkage"</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="8" priority="13" operator="beginsWith" text="Fusion">
+      <formula>LEFT(H3,LEN("Fusion"))="Fusion"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text=",">
       <formula>NOT(ISERROR(SEARCH(",", H3)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="11" priority="13" operator="beginsWith" text="Fusion">
-      <formula>LEFT(H3,LEN("Fusion"))="Fusion"</formula>
-    </cfRule>
-    <cfRule type="beginsWith" dxfId="10" priority="14" operator="beginsWith" text="Fission">
-      <formula>LEFT(H3,LEN("Fission"))="Fission"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="15">
-      <formula>H3="Missing Data"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="16">
+    <cfRule type="expression" dxfId="6" priority="16">
       <formula>H3="Death"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="17">
-      <formula>H3="Shrinkage"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="18">
-      <formula>H3="Growth"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="19">
-      <formula>H3="Recruitment"</formula>
+    <cfRule type="expression" dxfId="5" priority="15">
+      <formula>H3="Missing Data"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:M2">
-    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="FI">
-      <formula>LEFT(I2,LEN("FI"))="FI"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Missing data">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Missing data">
       <formula>NOT(ISERROR(SEARCH("Missing data",I2)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="2" priority="4" operator="beginsWith" text="R">
+    <cfRule type="beginsWith" dxfId="3" priority="4" operator="beginsWith" text="R">
       <formula>LEFT(I2,LEN("R"))="R"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="NA">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="NA">
       <formula>NOT(ISERROR(SEARCH("NA",I2)))</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="FI">
+      <formula>LEFT(I2,LEN("FI"))="FI"</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="D">
       <formula>NOT(ISERROR(SEARCH("D",I2)))</formula>
